--- a/src/ele.xlsx
+++ b/src/ele.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eleme/Desktop/模版/未命名文件夹/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35FAC7EB-EBC8-7F48-8906-4BA7C9ECDEB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B785E61-57A4-B047-8942-78A09D39ECFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{E9F034DC-D0AE-3341-A436-E647184B2AE2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7197" uniqueCount="2812">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7193" uniqueCount="2811">
   <si>
     <t>水果</t>
   </si>
@@ -8420,6 +8420,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>规格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>重量</t>
     <rPh sb="0" eb="2">
       <t>zhong'lian</t>
@@ -8431,27 +8435,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>产地</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>净含量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>品种</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>包装规格</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>售价</t>
-    <rPh sb="0" eb="2">
-      <t>shou'ji</t>
-    </rPh>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>库存</t>
@@ -8476,6 +8460,10 @@
     <rPh sb="0" eb="7">
       <t>men'diashang pi</t>
     </rPh>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>规格自定义ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -8797,6 +8785,109 @@
         <charset val="134"/>
       </rPr>
       <t>在提交时勾选了使用平台商品库信息，则未填写类目时优先使用平台商品类目。没有平台商品类目会由系统预测类目。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>（1）创建非多规格，</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>选填</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+（2）创建多规格，</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>必填，</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>同一个多规格商品请务必填写同一个商品名称</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+  (3) 有销售属性时，支持指定销售属性(如</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>“规格:256G”)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>根据组合方式进行录入；如果说需要多个维度的销售属性，需要录入带“#”的属分隔符（如</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>“规格:256G#颜色分类:白色”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>），系统会自动组合为对应的SKU，否则按照单规格进行录，具体场景如下：                                                        A. 填写的销售属性需要在当前类目下存在
+B. “#”不支持作为属性值录入，若商家需要录入含#的属性值，Excel不支持，需要从单个商品创建页录入；
+C. 若单元格中无分隔符，如"颜色分类:白色"则解析为只有一个属性值</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -8938,33 +9029,6 @@
     <r>
       <rPr>
         <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="4"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>选填，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="4"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-若在提交时勾选了使用平台商品库信息，未填写时会优先使用平台推荐值</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="微软雅黑"/>
@@ -8985,10 +9049,6 @@
       <t>单位（元）
 最多2位小数</t>
     </r>
-    <rPh sb="0" eb="3">
-      <t>bi'tiadan'we</t>
-    </rPh>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -9016,7 +9076,7 @@
     <rPh sb="0" eb="14">
       <t>bi ti a</t>
     </rPh>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -9068,8 +9128,7 @@
       </rPr>
       <t xml:space="preserve">
 请填写“上架/下架”，
-默认为上架。
-BD代操作无需填写，任务成功后商品状态默认调整为下架，商家操作可忽略此内容</t>
+默认为上架</t>
     </r>
     <rPh sb="0" eb="20">
       <t>xuan ti aqing tian xishang ji</t>
@@ -9102,6 +9161,31 @@
     <rPh sb="0" eb="2">
       <t>xuan ti ashang ja</t>
     </rPh>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>选填</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+不超过50个字符</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -9254,8 +9338,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">选填
-</t>
+      <t>选填</t>
     </r>
     <r>
       <rPr>
@@ -9265,7 +9348,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>（单位：元，包装费范围0~99999，最多支持两位小数）</t>
+      <t>（0~99999，最多支持两位小数）</t>
     </r>
     <r>
       <rPr>
@@ -9557,7 +9640,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="36">
+  <fonts count="45">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -9606,12 +9689,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <color theme="1"/>
       <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
@@ -9627,7 +9705,117 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
@@ -9673,38 +9861,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
@@ -9716,6 +9872,13 @@
       <color theme="1"/>
       <name val="微软雅黑"/>
       <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -9792,15 +9955,6 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
@@ -9816,12 +9970,11 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="等线"/>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -9893,7 +10046,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -9918,80 +10071,116 @@
     <xf numFmtId="49" fontId="5" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="25" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="26" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="33" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="34" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="35" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="41" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -10002,7 +10191,7 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -10324,161 +10513,149 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="32.83203125" customWidth="1"/>
     <col min="2" max="2" width="40.83203125" customWidth="1"/>
     <col min="3" max="3" width="33.33203125" customWidth="1"/>
-    <col min="4" max="4" width="33.1640625" customWidth="1"/>
-    <col min="5" max="8" width="20.83203125" customWidth="1"/>
-    <col min="9" max="9" width="30.83203125" customWidth="1"/>
-    <col min="10" max="13" width="20.83203125" customWidth="1"/>
-    <col min="14" max="14" width="55.6640625" customWidth="1"/>
-    <col min="15" max="20" width="20.83203125" customWidth="1"/>
-    <col min="21" max="21" width="33" customWidth="1"/>
-    <col min="22" max="22" width="35" customWidth="1"/>
+    <col min="4" max="4" width="61.33203125" customWidth="1"/>
+    <col min="5" max="5" width="34.33203125" customWidth="1"/>
+    <col min="6" max="6" width="21" customWidth="1"/>
+    <col min="7" max="10" width="20.83203125" customWidth="1"/>
+    <col min="11" max="11" width="55.6640625" customWidth="1"/>
+    <col min="12" max="18" width="20.83203125" customWidth="1"/>
+    <col min="19" max="19" width="33" customWidth="1"/>
+    <col min="20" max="20" width="32.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="36" customFormat="1" ht="17">
+    <row r="1" spans="1:20" ht="17">
       <c r="A1" s="7" t="s">
         <v>2768</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="8" t="s">
         <v>2769</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="9" t="s">
         <v>2770</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="10" t="s">
         <v>2771</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="11" t="s">
         <v>2772</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="12" t="s">
         <v>2773</v>
       </c>
-      <c r="G1" s="35" t="s">
+      <c r="G1" s="13" t="s">
         <v>2774</v>
       </c>
-      <c r="H1" s="35" t="s">
+      <c r="H1" s="14" t="s">
         <v>2775</v>
       </c>
-      <c r="I1" s="35" t="s">
+      <c r="I1" s="15" t="s">
         <v>2776</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="16" t="s">
         <v>2777</v>
       </c>
-      <c r="K1" s="35" t="s">
+      <c r="K1" s="47" t="s">
+        <v>2808</v>
+      </c>
+      <c r="L1" s="17" t="s">
         <v>2778</v>
       </c>
-      <c r="L1" s="35" t="s">
+      <c r="M1" s="18" t="s">
         <v>2779</v>
       </c>
-      <c r="M1" s="35" t="s">
+      <c r="N1" s="19" t="s">
         <v>2780</v>
       </c>
-      <c r="N1" s="35" t="s">
+      <c r="O1" s="20" t="s">
+        <v>2781</v>
+      </c>
+      <c r="P1" s="21" t="s">
+        <v>2782</v>
+      </c>
+      <c r="Q1" s="22" t="s">
+        <v>2783</v>
+      </c>
+      <c r="R1" s="23" t="s">
+        <v>2784</v>
+      </c>
+      <c r="S1" s="24" t="s">
+        <v>2785</v>
+      </c>
+      <c r="T1" s="44" t="s">
+        <v>2805</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" ht="234">
+      <c r="A2" s="25" t="s">
+        <v>2786</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>2787</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>2788</v>
+      </c>
+      <c r="D2" s="28" t="s">
+        <v>2789</v>
+      </c>
+      <c r="E2" s="29" t="s">
+        <v>2790</v>
+      </c>
+      <c r="F2" s="30" t="s">
+        <v>2791</v>
+      </c>
+      <c r="G2" s="31" t="s">
+        <v>2792</v>
+      </c>
+      <c r="H2" s="32" t="s">
+        <v>2793</v>
+      </c>
+      <c r="I2" s="33" t="s">
+        <v>2794</v>
+      </c>
+      <c r="J2" s="34" t="s">
+        <v>2795</v>
+      </c>
+      <c r="K2" s="25" t="s">
         <v>2809</v>
       </c>
-      <c r="O1" s="7" t="s">
-        <v>2781</v>
-      </c>
-      <c r="P1" s="7" t="s">
-        <v>2782</v>
-      </c>
-      <c r="Q1" s="7" t="s">
-        <v>2783</v>
-      </c>
-      <c r="R1" s="7" t="s">
-        <v>2784</v>
-      </c>
-      <c r="S1" s="35" t="s">
-        <v>2785</v>
-      </c>
-      <c r="T1" s="35" t="s">
-        <v>2786</v>
-      </c>
-      <c r="U1" s="35" t="s">
-        <v>2787</v>
-      </c>
-      <c r="V1" s="31" t="s">
+      <c r="L2" s="35" t="s">
+        <v>2796</v>
+      </c>
+      <c r="M2" s="36" t="s">
+        <v>2797</v>
+      </c>
+      <c r="N2" s="37" t="s">
+        <v>2798</v>
+      </c>
+      <c r="O2" s="38" t="s">
+        <v>2799</v>
+      </c>
+      <c r="P2" s="39" t="s">
+        <v>2800</v>
+      </c>
+      <c r="Q2" s="40" t="s">
+        <v>2801</v>
+      </c>
+      <c r="R2" s="41" t="s">
+        <v>2802</v>
+      </c>
+      <c r="S2" s="42" t="s">
+        <v>2803</v>
+      </c>
+      <c r="T2" s="25" t="s">
         <v>2806</v>
       </c>
     </row>
-    <row r="2" spans="1:22" ht="234">
-      <c r="A2" s="10" t="s">
-        <v>2788</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>2789</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>2790</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>2791</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>2792</v>
-      </c>
-      <c r="F2" s="15" t="s">
-        <v>2793</v>
-      </c>
-      <c r="G2" s="16" t="s">
-        <v>2793</v>
-      </c>
-      <c r="H2" s="17" t="s">
-        <v>2793</v>
-      </c>
-      <c r="I2" s="18" t="s">
-        <v>2793</v>
-      </c>
-      <c r="J2" s="19" t="s">
-        <v>2794</v>
-      </c>
-      <c r="K2" s="20" t="s">
-        <v>2795</v>
-      </c>
-      <c r="L2" s="21" t="s">
-        <v>2796</v>
-      </c>
-      <c r="M2" s="22" t="s">
-        <v>2797</v>
-      </c>
-      <c r="N2" s="32" t="s">
-        <v>2810</v>
-      </c>
-      <c r="O2" s="23" t="s">
-        <v>2798</v>
-      </c>
-      <c r="P2" s="24" t="s">
-        <v>2799</v>
-      </c>
-      <c r="Q2" s="25" t="s">
-        <v>2800</v>
-      </c>
-      <c r="R2" s="26" t="s">
-        <v>2801</v>
-      </c>
-      <c r="S2" s="27" t="s">
-        <v>2802</v>
-      </c>
-      <c r="T2" s="28" t="s">
-        <v>2803</v>
-      </c>
-      <c r="U2" s="29" t="s">
+    <row r="3" spans="1:20">
+      <c r="A3" s="43" t="s">
         <v>2804</v>
-      </c>
-      <c r="V2" s="32" t="s">
-        <v>2807</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22">
-      <c r="A3" s="30" t="s">
-        <v>2805</v>
       </c>
     </row>
   </sheetData>
@@ -10489,7 +10666,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55F27A15-EAB4-594D-973A-890B046FD009}">
-  <dimension ref="A1:V2382"/>
+  <dimension ref="A1:T2382"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="24.1640625" customWidth="1"/>
@@ -10498,12 +10675,11 @@
     <col min="4" max="4" width="36.6640625" customWidth="1"/>
     <col min="5" max="5" width="37.6640625" customWidth="1"/>
     <col min="6" max="6" width="21.33203125" customWidth="1"/>
-    <col min="14" max="14" width="55.6640625" customWidth="1"/>
-    <col min="20" max="20" width="33" customWidth="1"/>
-    <col min="22" max="22" width="35" customWidth="1"/>
+    <col min="11" max="11" width="55.6640625" customWidth="1"/>
+    <col min="20" max="20" width="32.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="36" customFormat="1" ht="23" customHeight="1">
+    <row r="1" spans="1:20" ht="23" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>2725</v>
       </c>
@@ -10522,11 +10698,11 @@
       <c r="F1" s="6" t="s">
         <v>2730</v>
       </c>
-      <c r="N1" s="36" t="s">
-        <v>2809</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22" ht="234">
+      <c r="K1" s="48" t="s">
+        <v>2808</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" ht="234">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -10545,14 +10721,14 @@
       <c r="F2">
         <v>201220135</v>
       </c>
-      <c r="N2" s="34" t="s">
-        <v>2811</v>
-      </c>
-      <c r="V2" s="33" t="s">
-        <v>2808</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22">
+      <c r="K2" s="46" t="s">
+        <v>2810</v>
+      </c>
+      <c r="T2" s="45" t="s">
+        <v>2807</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -10572,7 +10748,7 @@
         <v>201227826</v>
       </c>
     </row>
-    <row r="4" spans="1:22">
+    <row r="4" spans="1:20">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -10592,7 +10768,7 @@
         <v>201217738</v>
       </c>
     </row>
-    <row r="5" spans="1:22">
+    <row r="5" spans="1:20">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -10612,7 +10788,7 @@
         <v>201219835</v>
       </c>
     </row>
-    <row r="6" spans="1:22">
+    <row r="6" spans="1:20">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -10632,7 +10808,7 @@
         <v>201230729</v>
       </c>
     </row>
-    <row r="7" spans="1:22">
+    <row r="7" spans="1:20">
       <c r="A7" t="s">
         <v>0</v>
       </c>
@@ -10652,7 +10828,7 @@
         <v>202033907</v>
       </c>
     </row>
-    <row r="8" spans="1:22">
+    <row r="8" spans="1:20">
       <c r="A8" t="s">
         <v>0</v>
       </c>
@@ -10672,7 +10848,7 @@
         <v>201218438</v>
       </c>
     </row>
-    <row r="9" spans="1:22">
+    <row r="9" spans="1:20">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -10692,7 +10868,7 @@
         <v>201228833</v>
       </c>
     </row>
-    <row r="10" spans="1:22">
+    <row r="10" spans="1:20">
       <c r="A10" t="s">
         <v>0</v>
       </c>
@@ -10712,7 +10888,7 @@
         <v>201218933</v>
       </c>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:20">
       <c r="A11" t="s">
         <v>0</v>
       </c>
@@ -10732,7 +10908,7 @@
         <v>201222646</v>
       </c>
     </row>
-    <row r="12" spans="1:22">
+    <row r="12" spans="1:20">
       <c r="A12" t="s">
         <v>0</v>
       </c>
@@ -10752,7 +10928,7 @@
         <v>201227537</v>
       </c>
     </row>
-    <row r="13" spans="1:22">
+    <row r="13" spans="1:20">
       <c r="A13" t="s">
         <v>0</v>
       </c>
@@ -10772,7 +10948,7 @@
         <v>201218834</v>
       </c>
     </row>
-    <row r="14" spans="1:22">
+    <row r="14" spans="1:20">
       <c r="A14" t="s">
         <v>0</v>
       </c>
@@ -10792,7 +10968,7 @@
         <v>201232627</v>
       </c>
     </row>
-    <row r="15" spans="1:22">
+    <row r="15" spans="1:20">
       <c r="A15" t="s">
         <v>0</v>
       </c>
@@ -10812,7 +10988,7 @@
         <v>201220133</v>
       </c>
     </row>
-    <row r="16" spans="1:22">
+    <row r="16" spans="1:20">
       <c r="A16" t="s">
         <v>0</v>
       </c>
